--- a/ios/localizzazione/NEAT_store_tradotto.xlsx
+++ b/ios/localizzazione/NEAT_store_tradotto.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>In walking minutes and kilometres</t>
+          <t>In walking minutes and kilometers</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">

--- a/ios/localizzazione/NEAT_store_tradotto.xlsx
+++ b/ios/localizzazione/NEAT_store_tradotto.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>In walking minutes and kilometers</t>
+          <t>In walking minutes and distance</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1449,7 +1449,11 @@
         <f>"EN: "&amp;LEN(F10)&amp;CHAR(10)&amp;"ES: "&amp;LEN(G10)&amp;CHAR(10)&amp;"FR: "&amp;LEN(H10)&amp;CHAR(10)&amp;"DE: "&amp;LEN(I10)&amp;CHAR(10)&amp;"PT-BR: "&amp;LEN(J10)&amp;CHAR(10)&amp;"JA: "&amp;LEN(K10)&amp;CHAR(10)&amp;"KO: "&amp;LEN(L10)&amp;CHAR(10)&amp;"ZH-Hans: "&amp;LEN(M10)&amp;CHAR(10)&amp;"ZH-Hant: "&amp;LEN(N10)</f>
         <v/>
       </c>
-      <c r="P10" s="6" t="n"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>COORDINAMENTO: EN neutra (miglia negli USA/UK, km altrove).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">

--- a/ios/localizzazione/NEAT_store_tradotto.xlsx
+++ b/ios/localizzazione/NEAT_store_tradotto.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Quanti passi ti mancano oggi? NEAT te lo dice in un colpo d'occhio. I tuoi dati restano sul tuo iPhone.</t>
+          <t>Quanti passi ti mancano oggi? NEAT te lo dice in un colpo d'occhio. I tuoi dati sono solo tuoi.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -928,7 +928,7 @@
 • Quanti ne mancano al tuo obiettivo.
 • Quanti minuti di camminata servono per raggiungerlo, alla velocità che scegli.
 Ogni giorno a obiettivo allunga la tua serie. Lo storico ti mostra settimane, mesi e record. Un promemoria la sera, se manca ancora qualcosa. E i widget ti tengono aggiornato senza aprire l'app.
-I tuoi dati restano sul tuo iPhone. NEAT legge soltanto: niente account, niente pubblicità, niente tracciamento. Nessun dato lascia il telefono.
+I tuoi dati sono solo tuoi. NEAT legge soltanto: niente account, niente pubblicità, niente tracciamento. Serie e impostazioni si salvano nel tuo iCloud, mai su server di altri. Cambi iPhone? Ritrovi la tua serie.
 Ogni passo conta.</t>
         </is>
       </c>

--- a/ios/localizzazione/NEAT_store_tradotto.xlsx
+++ b/ios/localizzazione/NEAT_store_tradotto.xlsx
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>I TUOI DATI RESTANO SUL TUO IPHONE</t>
+          <t>I TUOI DATI SONO SOLO TUOI</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Nessun dato lascia il telefono</t>
+          <t>Nessuno li vede, nemmeno noi</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">

--- a/ios/localizzazione/NEAT_store_tradotto.xlsx
+++ b/ios/localizzazione/NEAT_store_tradotto.xlsx
@@ -818,7 +818,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="108" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>store.promo</t>
@@ -846,60 +846,68 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>How many steps left today? NEAT shows you at a glance. Your data stays on your iPhone.</t>
+          <t xml:space="preserve">How many steps left today? NEAT shows you at a glance. Your data is yours alone.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>¿Cuántos pasos te faltan hoy? NEAT te lo dice de un vistazo. Tus datos se quedan en tu iPhone.</t>
+          <t xml:space="preserve">¿Cuántos pasos te faltan hoy? NEAT te lo dice de un vistazo. Tus datos son solo tuyos.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Combien de pas te reste-t-il aujourd’hui ? NEAT te le dit en un clin d’œil. Tes données restent sur ton iPhone.</t>
+          <t xml:space="preserve">Combien de pas te reste-t-il aujourd’hui ? NEAT te le dit en un clin d’œil. Tes données, rien qu’à toi.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Wie viele Schritte fehlen dir heute? NEAT zeigt es dir auf einen Blick. Deine Daten bleiben auf dem iPhone.</t>
+          <t xml:space="preserve">Wie viele Schritte fehlen dir heute? NEAT zeigt es dir auf einen Blick. Deine Daten gehören nur dir.</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Quantos passos faltam hoje? O NEAT mostra num relance. Seus dados ficam no seu iPhone.</t>
+          <t xml:space="preserve">Quantos passos faltam hoje? O NEAT mostra num relance. Seus dados são só seus.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>今日の目標まで、あと何歩？NEATならひと目でわかります。あなたのデータは、あなたのiPhoneの中に。</t>
+          <t xml:space="preserve">今日の目標まで、あと何歩？NEATならひと目でわかります。あなたのデータは、あなただけのもの。</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>오늘 몇 걸음 더 걸어야 할까요? NEAT에서 한눈에 확인하세요. 내 데이터는 내 iPhone에 그대로.</t>
+          <t xml:space="preserve">오늘 몇 걸음 더 걸어야 할까요? NEAT에서 한눈에 확인하세요. 내 데이터는 나만의 것.</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>今天还差多少步？NEAT让你一目了然。你的数据留在你的iPhone上。</t>
+          <t xml:space="preserve">今天还差多少步？NEAT让你一目了然。你的数据只属于你。</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>今天還差幾步？NEAT讓你一目了然。你的資料留在你的iPhone上。</t>
-        </is>
-      </c>
-      <c r="O4" s="6">
+          <t xml:space="preserve">今天還差幾步？NEAT讓你一目了然。你的資料只屬於你。</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="str">
         <f>"EN: "&amp;LEN(F4)&amp;CHAR(10)&amp;"ES: "&amp;LEN(G4)&amp;CHAR(10)&amp;"FR: "&amp;LEN(H4)&amp;CHAR(10)&amp;"DE: "&amp;LEN(I4)&amp;CHAR(10)&amp;"PT-BR: "&amp;LEN(J4)&amp;CHAR(10)&amp;"JA: "&amp;LEN(K4)&amp;CHAR(10)&amp;"KO: "&amp;LEN(L4)&amp;CHAR(10)&amp;"ZH-Hans: "&amp;LEN(M4)&amp;CHAR(10)&amp;"ZH-Hant: "&amp;LEN(N4)</f>
-        <v/>
+        <v>EN: 80
+ES: 86
+FR: 103
+DE: 100
+PT-BR: 78
+JA: 47
+KO: 50
+ZH-Hans: 28
+ZH-Hant: 27</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Promessa identica a shot6.title, salvo maiuscole, punteggiatura finale e indicatore di a capo. DE: «auf dem iPhone» per il limite del titolo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="420" customHeight="1">
+          <t xml:space="preserve">Nuova promessa 1.1: dati solo dell’utente. Stessa frase in descrizione e shot6.title, salvo maiuscole, punto finale e separatore di riga. Resto del promozionale invariato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="276" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>store.description</t>
@@ -934,115 +942,123 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>How many steps have I taken today? How many do I have left? How much longer do I need to walk?
+          <t xml:space="preserve">How many steps have I taken today? How many do I have left? How much longer do I need to walk?
 NEAT answers these three questions at a glance.
 • Today's steps, read from Health.
 • How many steps are left to reach your goal.
 • How many minutes of walking it takes to get there, at the speed you choose.
 Each day you reach your goal extends your streak. Your history shows weeks, months and records. An evening reminder if you still have steps to go. And widgets keep you up to date without opening the app.
-Your data stays on your iPhone. NEAT only reads: no account, no ads, no tracking. No data leaves your phone.
+Your data is yours alone. NEAT only reads: no account, no ads, no tracking. Your streak and settings are saved in your iCloud, never on other servers. Switching to another iPhone? Your streak is still there.
 Every step counts.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>¿Cuántos pasos he dado hoy? ¿Cuántos me faltan? ¿Cuánto más tengo que caminar?
+          <t xml:space="preserve">¿Cuántos pasos he dado hoy? ¿Cuántos me faltan? ¿Cuánto más tengo que caminar?
 NEAT responde a estas tres preguntas de un vistazo.
 • Los pasos de hoy, leídos de Salud.
 • Cuántos te faltan para llegar a tu meta.
 • Cuántos minutos necesitas caminar para alcanzarla, a la velocidad que elijas.
 Cada día que alcanzas tu meta alarga tu racha. El historial te muestra semanas, meses y récords. Un recordatorio por la tarde si aún te faltan pasos. Y los widgets te mantienen al día sin abrir la app.
-Tus datos se quedan en tu iPhone. NEAT solo lee: sin cuenta, sin anuncios, sin rastreo. Ningún dato sale del teléfono.
+Tus datos son solo tuyos. NEAT solo lee: sin cuenta, sin anuncios, sin rastreo. Tu racha y tus ajustes se guardan en tu iCloud, nunca en otros servidores. ¿Cambias de iPhone? Recuperas tu racha.
 Cada paso cuenta.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Combien de pas ai-je faits aujourd’hui ? Combien m’en reste-t-il ? Combien de temps dois-je encore marcher ?
+          <t xml:space="preserve">Combien de pas ai-je faits aujourd’hui ? Combien m’en reste-t-il ? Combien de temps dois-je encore marcher ?
 NEAT répond à ces trois questions en un clin d’œil.
 • Les pas du jour, lus dans Santé.
 • Le nombre de pas restants pour atteindre ton objectif.
 • Les minutes de marche nécessaires pour l’atteindre, à la vitesse de ton choix.
 Chaque jour où tu atteins ton objectif prolonge ta série. L’historique affiche les semaines, les mois et les records. Un rappel le soir s’il te reste des pas à faire. Et les widgets te tiennent au courant sans ouvrir l’app.
-Tes données restent sur ton iPhone. NEAT ne fait que lire : aucun compte, aucune pub, aucun suivi. Aucune donnée ne quitte ton téléphone.
+Tes données, rien qu’à toi. NEAT ne fait que lire : aucun compte, aucune pub, aucun suivi. Ta série et tes réglages sont enregistrés dans ton iCloud, jamais sur d’autres serveurs. Tu changes d’iPhone ? Tu retrouves ta série.
 Chaque pas compte.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Wie viele Schritte bin ich heute gegangen? Wie viele fehlen mir noch? Wie lange muss ich noch gehen?
+          <t xml:space="preserve">Wie viele Schritte bin ich heute gegangen? Wie viele fehlen mir noch? Wie lange muss ich noch gehen?
 NEAT beantwortet diese drei Fragen auf einen Blick.
 • Die heutigen Schritte, aus Health gelesen.
 • Wie viele Schritte dir noch bis zu deinem Ziel fehlen.
 • Wie viele Gehminuten du dafür brauchst, bei deinem gewählten Tempo.
 Jeder Tag, an dem du dein Ziel erreichst, verlängert deine Serie. Der Verlauf zeigt dir Wochen, Monate und Rekorde. Eine Erinnerung am Abend, wenn noch Schritte fehlen. Und Widgets halten dich auf dem Laufenden, ohne die App zu öffnen.
-Deine Daten bleiben auf dem iPhone. NEAT liest nur: kein Konto, keine Werbung, kein Tracking. Keine Daten verlassen dein Telefon.
+Deine Daten gehören nur dir. NEAT liest nur: kein Konto, keine Werbung, kein Tracking. Deine Serie und Einstellungen werden in deiner iCloud gesichert, nie auf anderen Servern. Du wechselst dein iPhone? Deine Serie ist wieder da.
 Jeder Schritt zählt.</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Quantos passos dei hoje? Quantos faltam? Quanto ainda preciso caminhar?
+          <t xml:space="preserve">Quantos passos dei hoje? Quantos faltam? Quanto ainda preciso caminhar?
 O NEAT responde a essas três perguntas num relance.
 • Os passos de hoje, lidos do Saúde.
 • Quantos faltam para alcançar sua meta.
 • Quantos minutos de caminhada são necessários para alcançá-la, na velocidade que você escolher.
 Cada dia em que você alcança sua meta aumenta sua sequência. O histórico mostra semanas, meses e recordes. Um lembrete à noite, se ainda faltarem passos. E os widgets mantêm você a par sem abrir o app.
-Seus dados ficam no seu iPhone. O NEAT só lê: sem conta, sem anúncios, sem rastreamento. Nenhum dado sai do celular.
+Seus dados são só seus. O NEAT só lê: sem conta, sem anúncios, sem rastreamento. Sua sequência e seus ajustes são salvos no seu iCloud, nunca em outros servidores. Vai trocar de iPhone? Sua sequência está lá.
 Cada passo conta.</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>今日は何歩歩いた？あと何歩？あとどれくらい歩けばいい？
+          <t xml:space="preserve">今日は何歩歩いた？あと何歩？あとどれくらい歩けばいい？
 NEATなら、この3つの答えがひと目でわかります。
 • ヘルスケアから読み取った今日の歩数。
 • 目標まであと何歩か。
 • 選んだ速度で、目標達成まであと何分歩けばいいか。
 目標を達成するたびに、連続記録が伸びます。履歴では週ごと、月ごとの歩数や記録を確認できます。まだ歩数が足りない日は、夜にリマインダーでお知らせ。ウィジェットなら、アプリを開かずに状況を確認できます。
-あなたのデータは、あなたのiPhoneの中に。NEATは読み取り専用。アカウントも、広告も、トラッキングもありません。データがスマートフォンの外に出ることはありません。
+あなたのデータは、あなただけのもの。NEATは読み取り専用。アカウントも、広告も、トラッキングもありません。連続記録と設定はあなたのiCloudに保存され、ほかのサーバーには保存されません。iPhoneを替えても、連続記録を引き継げます。
 一歩一歩が大切。</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>오늘 몇 걸음 걸었을까? 몇 걸음 남았을까? 얼마나 더 걸어야 할까?
+          <t xml:space="preserve">오늘 몇 걸음 걸었을까? 몇 걸음 남았을까? 얼마나 더 걸어야 할까?
 NEAT는 이 세 가지 질문의 답을 한눈에 보여줘요.
 • 건강 앱에서 읽어 온 오늘의 걸음 수.
 • 목표까지 남은 걸음 수.
 • 선택한 속도로 목표에 도달하려면 더 걸어야 하는 시간(분).
 목표를 달성할 때마다 연속 기록이 늘어나요. 기록에서 주별, 월별 걸음 수와 최고 기록을 확인하세요. 아직 걸음 수가 부족하면 저녁에 알림을 보내요. 위젯으로 앱을 열지 않고도 현황을 확인할 수 있어요.
-내 데이터는 내 iPhone에 그대로. NEAT는 읽기만 해요. 계정도, 광고도, 추적도 없어요. 어떤 데이터도 휴대폰 밖으로 나가지 않아요.
+내 데이터는 나만의 것. NEAT는 읽기만 해요. 계정도, 광고도, 추적도 없어요. 연속 기록과 설정은 내 iCloud에 저장되고, 다른 서버에는 저장되지 않아요. iPhone을 바꿔도 연속 기록을 되찾을 수 있어요.
 한 걸음 한 걸음이 소중해요.</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>今天走了多少步？还差多少步？还要走多久？
+          <t xml:space="preserve">今天走了多少步？还差多少步？还要走多久？
 NEAT让这三个问题的答案一目了然。
 • 从健康读取的今日步数。
 • 距离目标还差多少步。
 • 按你选择的速度，还要走多少分钟才能达标。
 每达标一天，连续记录就增加一天。历史记录按周、按月显示步数，还能查看最高纪录。如果还没达标，晚上会收到提醒。通过小组件，无需打开App就能查看进度。
-你的数据留在你的iPhone上。NEAT只读取数据：无需账号、没有广告、没有跟踪。任何数据都不会离开手机。
+你的数据只属于你。NEAT只读取数据：无需账号、没有广告、没有跟踪。连续记录和设置会保存在你的iCloud中，不会存到其他服务器。换了iPhone？你的连续记录还在。
 每一步都算数。</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>今天走了幾步？還差幾步？還要走多久？
+          <t xml:space="preserve">今天走了幾步？還差幾步？還要走多久？
 NEAT讓這三個問題的答案一目了然。
 • 從健康讀取的今日步數。
 • 距離目標還差幾步。
 • 按照你選擇的速度，還要走幾分鐘才能達標。
 每達標一天，連續紀錄就增加一天。歷史紀錄按週、按月顯示步數，也能查看最高紀錄。如果還沒達標，晚上會收到提醒。透過小工具，不用打開App就能查看進度。
-你的資料留在你的iPhone上。NEAT只讀取資料：不需帳號、沒有廣告、沒有追蹤。任何資料都不會離開手機。
+你的資料只屬於你。NEAT只讀取資料：不需帳號、沒有廣告、沒有追蹤。連續紀錄和設定會儲存在你的iCloud中，不會存到其他伺服器。換了iPhone？你的連續紀錄還在。
 每一步都算數。</t>
         </is>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="6" t="str">
         <f>"EN: "&amp;LEN(F5)&amp;CHAR(10)&amp;"ES: "&amp;LEN(G5)&amp;CHAR(10)&amp;"FR: "&amp;LEN(H5)&amp;CHAR(10)&amp;"DE: "&amp;LEN(I5)&amp;CHAR(10)&amp;"PT-BR: "&amp;LEN(J5)&amp;CHAR(10)&amp;"JA: "&amp;LEN(K5)&amp;CHAR(10)&amp;"KO: "&amp;LEN(L5)&amp;CHAR(10)&amp;"ZH-Hans: "&amp;LEN(M5)&amp;CHAR(10)&amp;"ZH-Hant: "&amp;LEN(N5)</f>
-        <v/>
+        <v>EN: 737
+ES: 710
+FR: 806
+DE: 816
+PT-BR: 732
+JA: 348
+KO: 402
+ZH-Hans: 261
+ZH-Hant: 258</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -1933,7 +1949,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="108" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>shot6.title</t>
@@ -1961,60 +1977,68 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>YOUR DATA STAYS / ON YOUR IPHONE</t>
+          <t xml:space="preserve">YOUR DATA / IS YOURS ALONE</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>TUS DATOS SE QUEDAN / EN TU IPHONE</t>
+          <t xml:space="preserve">TUS DATOS / SON SOLO TUYOS</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>TES DONNÉES RESTENT / SUR TON IPHONE</t>
+          <t xml:space="preserve">TES DONNÉES, / RIEN QU’À TOI</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>DEINE DATEN BLEIBEN / AUF DEM IPHONE</t>
+          <t xml:space="preserve">DEINE DATEN / GEHÖREN NUR DIR</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>SEUS DADOS FICAM / NO SEU IPHONE</t>
+          <t xml:space="preserve">SEUS DADOS / SÃO SÓ SEUS</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>あなたのデータは、 / あなたのiPhoneの中に</t>
+          <t xml:space="preserve">あなたのデータは、 / あなただけのもの</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>내 데이터는 / 내 iPhone에 그대로</t>
+          <t xml:space="preserve">내 데이터는 / 나만의 것</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>你的数据 / 留在你的iPhone上</t>
+          <t xml:space="preserve">你的数据 / 只属于你</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>你的資料 / 留在你的iPhone上</t>
-        </is>
-      </c>
-      <c r="O17" s="6">
+          <t xml:space="preserve">你的資料 / 只屬於你</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="str">
         <f>"EN: "&amp;LEN(F17)&amp;CHAR(10)&amp;"ES: "&amp;LEN(G17)&amp;CHAR(10)&amp;"FR: "&amp;LEN(H17)&amp;CHAR(10)&amp;"DE: "&amp;LEN(I17)&amp;CHAR(10)&amp;"PT-BR: "&amp;LEN(J17)&amp;CHAR(10)&amp;"JA: "&amp;LEN(K17)&amp;CHAR(10)&amp;"KO: "&amp;LEN(L17)&amp;CHAR(10)&amp;"ZH-Hans: "&amp;LEN(M17)&amp;CHAR(10)&amp;"ZH-Hant: "&amp;LEN(N17)</f>
-        <v/>
+        <v>EN: 26
+ES: 26
+FR: 28
+DE: 29
+PT-BR: 24
+JA: 20
+KO: 14
+ZH-Hans: 11
+ZH-Hant: 11</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Stesse parole del promozionale; « / » per 2 righe. DE: forma breve coerente in promozionale e descrizione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t xml:space="preserve">Promessa 1.1 identica al promozionale e alla descrizione. Un solo separatore « / » per due righe in tutte le lingue, comprese JA/KO/ZH. Conteggi comprensivi del separatore; tutti entro 36.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="108" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>shot6.sub</t>
@@ -2042,56 +2066,64 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>No data leaves your phone</t>
+          <t xml:space="preserve">No one sees it, not even us</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Ningún dato sale del teléfono</t>
+          <t xml:space="preserve">Nadie los ve, ni siquiera nosotros</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Aucune donnée ne quitte le mobile</t>
+          <t xml:space="preserve">Personne ne les voit, nous inclus</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Keine Daten verlassen dein Telefon</t>
+          <t xml:space="preserve">Keiner sieht sie, auch wir nicht</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Nenhum dado sai do celular</t>
+          <t xml:space="preserve">Ninguém vê, nem mesmo nós</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>データはスマートフォンの外に出ません</t>
+          <t xml:space="preserve">誰も見ません。私たち開発者も</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>어떤 데이터도 휴대폰 밖으로 나가지 않아요</t>
+          <t xml:space="preserve">아무도 보지 않아요. 저희도요</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>任何数据都不会离开手机</t>
+          <t xml:space="preserve">没人能看到，连我们也不能</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>任何資料都不會離開手機</t>
-        </is>
-      </c>
-      <c r="O18" s="6">
+          <t xml:space="preserve">沒有人看得到，連我們也不行</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="str">
         <f>"EN: "&amp;LEN(F18)&amp;CHAR(10)&amp;"ES: "&amp;LEN(G18)&amp;CHAR(10)&amp;"FR: "&amp;LEN(H18)&amp;CHAR(10)&amp;"DE: "&amp;LEN(I18)&amp;CHAR(10)&amp;"PT-BR: "&amp;LEN(J18)&amp;CHAR(10)&amp;"JA: "&amp;LEN(K18)&amp;CHAR(10)&amp;"KO: "&amp;LEN(L18)&amp;CHAR(10)&amp;"ZH-Hans: "&amp;LEN(M18)&amp;CHAR(10)&amp;"ZH-Hant: "&amp;LEN(N18)</f>
-        <v/>
+        <v>EN: 27
+ES: 34
+FR: 33
+DE: 32
+PT-BR: 25
+JA: 14
+KO: 16
+ZH-Hans: 12
+ZH-Hant: 13</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Italiano e 9 traduzioni aggiornati su istruzione esplicita: «Nessun dato lascia il telefono». FR: «mobile» per il limite di 34.</t>
+          <t xml:space="preserve">Promessa 1.1: nessuno vede i dati, nemmeno chi sviluppa NEAT. FR: «nous inclus» rende «nemmeno noi» entro 34 caratteri. JA: 開発者 chiarisce chi è «noi». Tutte le lingue entro 34.</t>
         </is>
       </c>
     </row>
